--- a/Data/mm_yy.xlsx
+++ b/Data/mm_yy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156D2DA2-8ABB-4D77-B97D-8D19FC95023D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21C856C6-2E97-488D-AC4F-0EAADEA7B44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Leiðbeiningar" sheetId="10" r:id="rId1"/>
@@ -787,23 +787,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{136D6514-B495-48D4-AD56-9541C4FDE3F6}">
   <dimension ref="B1:O24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.1796875" customWidth="1"/>
-    <col min="12" max="12" width="9.36328125" customWidth="1"/>
+    <col min="1" max="1" width="4.21875" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>92</v>
       </c>
@@ -818,7 +818,7 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>93</v>
       </c>
@@ -833,7 +833,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>88</v>
       </c>
@@ -848,12 +848,12 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="8" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="12" t="s">
         <v>90</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -875,12 +875,12 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>94</v>
       </c>
@@ -894,7 +894,7 @@
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>95</v>
       </c>
@@ -908,7 +908,7 @@
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>96</v>
       </c>
@@ -922,12 +922,12 @@
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>98</v>
       </c>
@@ -939,12 +939,12 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
         <v>103</v>
       </c>
@@ -962,12 +962,12 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="5" t="s">
         <v>100</v>
       </c>
@@ -991,24 +991,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L100"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L151"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="5"/>
-    <col min="2" max="2" width="13.26953125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" customWidth="1"/>
-    <col min="8" max="8" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="5"/>
+    <col min="2" max="2" width="13.21875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
@@ -1046,7 +1046,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
       <c r="D2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1075,7 +1078,10 @@
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
       <c r="D3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1104,7 +1110,10 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
       <c r="D4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1133,7 +1142,10 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
       <c r="D5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1162,7 +1174,10 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
       <c r="D6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1191,7 +1206,10 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
       <c r="D7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1220,7 +1238,10 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
       <c r="D8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1249,7 +1270,10 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
       <c r="D9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1278,7 +1302,10 @@
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
       <c r="D10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1307,7 +1334,10 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
       <c r="D11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1336,7 +1366,10 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
       <c r="D12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1365,7 +1398,10 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
       <c r="D13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1394,7 +1430,10 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
       <c r="D14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1423,7 +1462,10 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
       <c r="D15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1452,7 +1494,10 @@
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
       <c r="D16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1481,7 +1526,10 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
       <c r="D17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1510,7 +1558,10 @@
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
     </row>
-    <row r="18" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
       <c r="D18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1539,7 +1590,10 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
       <c r="D19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1568,7 +1622,10 @@
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
     </row>
-    <row r="20" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
       <c r="D20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1597,7 +1654,10 @@
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
       <c r="D21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1626,7 +1686,10 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>21</v>
+      </c>
       <c r="D22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1655,7 +1718,10 @@
       <c r="K22" s="7"/>
       <c r="L22" s="8"/>
     </row>
-    <row r="23" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
       <c r="D23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1684,7 +1750,10 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
     </row>
-    <row r="24" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <v>23</v>
+      </c>
       <c r="D24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1713,7 +1782,10 @@
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
-    <row r="25" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
       <c r="D25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1742,7 +1814,10 @@
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
-    <row r="26" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
       <c r="D26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1771,7 +1846,10 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
-    <row r="27" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
       <c r="D27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1800,7 +1878,10 @@
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
     </row>
-    <row r="28" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
       <c r="D28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1829,7 +1910,10 @@
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
       <c r="D29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1858,7 +1942,10 @@
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
-    <row r="30" spans="4:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
       <c r="D30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1887,7 +1974,10 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" spans="4:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
       <c r="D31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1916,7 +2006,10 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
-    <row r="32" spans="4:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
       <c r="D32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1945,7 +2038,10 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
     </row>
-    <row r="33" spans="4:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
       <c r="D33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -1974,7 +2070,10 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
-    <row r="34" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
       <c r="D34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2003,7 +2102,10 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
-    <row r="35" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
       <c r="D35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2032,7 +2134,10 @@
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
     </row>
-    <row r="36" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
       <c r="D36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2061,7 +2166,10 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
     </row>
-    <row r="37" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
       <c r="D37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2090,7 +2198,10 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
     </row>
-    <row r="38" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
+        <v>37</v>
+      </c>
       <c r="D38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2119,7 +2230,10 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
     </row>
-    <row r="39" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
       <c r="D39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2148,7 +2262,10 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="5">
+        <v>39</v>
+      </c>
       <c r="D40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2177,7 +2294,10 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
       <c r="D41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2206,7 +2326,10 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
       <c r="D42">
         <f>_xlfn.XLOOKUP(C42,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2235,7 +2358,10 @@
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
       <c r="D43">
         <f>_xlfn.XLOOKUP(C43,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2264,7 +2390,10 @@
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
+        <v>43</v>
+      </c>
       <c r="D44">
         <f>_xlfn.XLOOKUP(C44,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2293,7 +2422,10 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
       <c r="D45">
         <f>_xlfn.XLOOKUP(C45,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2322,7 +2454,10 @@
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
+        <v>45</v>
+      </c>
       <c r="D46">
         <f>_xlfn.XLOOKUP(C46,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2351,7 +2486,10 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
       <c r="D47">
         <f>_xlfn.XLOOKUP(C47,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2380,7 +2518,10 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
       <c r="D48">
         <f>_xlfn.XLOOKUP(C48,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2409,7 +2550,10 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
       <c r="D49">
         <f>_xlfn.XLOOKUP(C49,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2438,7 +2582,10 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
+        <v>49</v>
+      </c>
       <c r="D50">
         <f>_xlfn.XLOOKUP(C50,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2467,7 +2614,10 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
       <c r="D51">
         <f>_xlfn.XLOOKUP(C51,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2496,7 +2646,10 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
+        <v>51</v>
+      </c>
       <c r="D52">
         <f>_xlfn.XLOOKUP(C52,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2525,7 +2678,10 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
       <c r="D53">
         <f>_xlfn.XLOOKUP(C53,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2554,7 +2710,10 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
+        <v>53</v>
+      </c>
       <c r="D54">
         <f>_xlfn.XLOOKUP(C54,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2583,7 +2742,10 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
       <c r="D55">
         <f>_xlfn.XLOOKUP(C55,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2612,7 +2774,10 @@
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
     </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
+        <v>55</v>
+      </c>
       <c r="D56">
         <f>_xlfn.XLOOKUP(C56,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2641,7 +2806,10 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
     </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
       <c r="D57">
         <f>_xlfn.XLOOKUP(C57,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2670,7 +2838,10 @@
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
     </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
+        <v>57</v>
+      </c>
       <c r="D58">
         <f>_xlfn.XLOOKUP(C58,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2699,7 +2870,10 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
       <c r="D59">
         <f>_xlfn.XLOOKUP(C59,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2728,7 +2902,10 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
+        <v>59</v>
+      </c>
       <c r="D60">
         <f>_xlfn.XLOOKUP(C60,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2757,7 +2934,10 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
     </row>
-    <row r="61" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
       <c r="D61">
         <f>_xlfn.XLOOKUP(C61,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2786,7 +2966,10 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
     </row>
-    <row r="62" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
+        <v>61</v>
+      </c>
       <c r="D62">
         <f>_xlfn.XLOOKUP(C62,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2815,7 +2998,10 @@
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
     </row>
-    <row r="63" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="5">
+        <v>62</v>
+      </c>
       <c r="D63">
         <f>_xlfn.XLOOKUP(C63,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2844,7 +3030,10 @@
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
     </row>
-    <row r="64" spans="4:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
+        <v>63</v>
+      </c>
       <c r="D64">
         <f>_xlfn.XLOOKUP(C64,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2870,7 +3059,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
       <c r="D65">
         <f>_xlfn.XLOOKUP(C65,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2896,7 +3088,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="5">
+        <v>65</v>
+      </c>
       <c r="D66">
         <f>_xlfn.XLOOKUP(C66,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2922,7 +3117,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
       <c r="D67">
         <f>_xlfn.XLOOKUP(C67,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2948,7 +3146,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="5">
+        <v>67</v>
+      </c>
       <c r="D68">
         <f>_xlfn.XLOOKUP(C68,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -2974,7 +3175,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="5">
+        <v>68</v>
+      </c>
       <c r="D69">
         <f>_xlfn.XLOOKUP(C69,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3000,7 +3204,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="5">
+        <v>69</v>
+      </c>
       <c r="D70">
         <f>_xlfn.XLOOKUP(C70,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3026,7 +3233,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
       <c r="D71">
         <f>_xlfn.XLOOKUP(C71,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3052,7 +3262,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="5">
+        <v>71</v>
+      </c>
       <c r="D72">
         <f>_xlfn.XLOOKUP(C72,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3078,7 +3291,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
       <c r="D73">
         <f>_xlfn.XLOOKUP(C73,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3104,7 +3320,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="5">
+        <v>73</v>
+      </c>
       <c r="D74">
         <f>_xlfn.XLOOKUP(C74,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3130,7 +3349,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
       <c r="D75">
         <f>_xlfn.XLOOKUP(C75,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3156,7 +3378,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="5">
+        <v>75</v>
+      </c>
       <c r="D76">
         <f>_xlfn.XLOOKUP(C76,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3182,7 +3407,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
       <c r="D77">
         <f>_xlfn.XLOOKUP(C77,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3208,7 +3436,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="5">
+        <v>77</v>
+      </c>
       <c r="D78">
         <f>_xlfn.XLOOKUP(C78,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3234,7 +3465,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
       <c r="D79">
         <f>_xlfn.XLOOKUP(C79,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3260,7 +3494,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="5">
+        <v>79</v>
+      </c>
       <c r="D80">
         <f>_xlfn.XLOOKUP(C80,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3286,7 +3523,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
       <c r="D81">
         <f>_xlfn.XLOOKUP(C81,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3312,7 +3552,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="5">
+        <v>81</v>
+      </c>
       <c r="D82">
         <f>_xlfn.XLOOKUP(C82,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3338,7 +3581,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
       <c r="D83">
         <f>_xlfn.XLOOKUP(C83,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3364,7 +3610,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="5">
+        <v>83</v>
+      </c>
       <c r="D84">
         <f>_xlfn.XLOOKUP(C84,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3390,7 +3639,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
       <c r="D85">
         <f>_xlfn.XLOOKUP(C85,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3416,7 +3668,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="5">
+        <v>85</v>
+      </c>
       <c r="D86">
         <f>_xlfn.XLOOKUP(C86,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3442,7 +3697,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
       <c r="D87">
         <f>_xlfn.XLOOKUP(C87,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3468,7 +3726,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" s="5">
+        <v>87</v>
+      </c>
       <c r="D88">
         <f>_xlfn.XLOOKUP(C88,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3494,7 +3755,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
       <c r="D89">
         <f>_xlfn.XLOOKUP(C89,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3520,7 +3784,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" s="5">
+        <v>89</v>
+      </c>
       <c r="D90">
         <f>_xlfn.XLOOKUP(C90,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3546,7 +3813,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
       <c r="D91">
         <f>_xlfn.XLOOKUP(C91,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3572,7 +3842,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="5">
+        <v>91</v>
+      </c>
       <c r="D92">
         <f>_xlfn.XLOOKUP(C92,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3598,7 +3871,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
       <c r="D93">
         <f>_xlfn.XLOOKUP(C93,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3624,7 +3900,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="5">
+        <v>93</v>
+      </c>
       <c r="D94">
         <f>_xlfn.XLOOKUP(C94,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3650,7 +3929,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
       <c r="D95">
         <f>_xlfn.XLOOKUP(C95,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3676,7 +3958,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" s="5">
+        <v>95</v>
+      </c>
       <c r="D96">
         <f>_xlfn.XLOOKUP(C96,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3702,7 +3987,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
       <c r="D97">
         <f>_xlfn.XLOOKUP(C97,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3728,7 +4016,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" s="5">
+        <v>97</v>
+      </c>
       <c r="D98">
         <f>_xlfn.XLOOKUP(C98,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3754,7 +4045,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="5">
+        <v>98</v>
+      </c>
       <c r="D99">
         <f>_xlfn.XLOOKUP(C99,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3780,7 +4074,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="5">
+        <v>99</v>
+      </c>
       <c r="D100">
         <f>_xlfn.XLOOKUP(C100,EventTypes!$A:$A,EventTypes!B:B)</f>
         <v>0</v>
@@ -3803,6 +4100,1485 @@
       </c>
       <c r="I100">
         <f>_xlfn.XLOOKUP(C100,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="5">
+        <v>100</v>
+      </c>
+      <c r="D101">
+        <f>_xlfn.XLOOKUP(C101,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <f>_xlfn.XLOOKUP(C101,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <f>_xlfn.XLOOKUP(C101,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <f>_xlfn.XLOOKUP(C101,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <f>_xlfn.XLOOKUP(C101,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <f>_xlfn.XLOOKUP(C101,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="5">
+        <v>101</v>
+      </c>
+      <c r="D102">
+        <f>_xlfn.XLOOKUP(C102,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <f>_xlfn.XLOOKUP(C102,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <f>_xlfn.XLOOKUP(C102,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <f>_xlfn.XLOOKUP(C102,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <f>_xlfn.XLOOKUP(C102,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <f>_xlfn.XLOOKUP(C102,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="5">
+        <v>102</v>
+      </c>
+      <c r="D103">
+        <f>_xlfn.XLOOKUP(C103,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <f>_xlfn.XLOOKUP(C103,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <f>_xlfn.XLOOKUP(C103,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <f>_xlfn.XLOOKUP(C103,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <f>_xlfn.XLOOKUP(C103,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <f>_xlfn.XLOOKUP(C103,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="5">
+        <v>103</v>
+      </c>
+      <c r="D104">
+        <f>_xlfn.XLOOKUP(C104,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <f>_xlfn.XLOOKUP(C104,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <f>_xlfn.XLOOKUP(C104,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <f>_xlfn.XLOOKUP(C104,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <f>_xlfn.XLOOKUP(C104,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <f>_xlfn.XLOOKUP(C104,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="5">
+        <v>104</v>
+      </c>
+      <c r="D105">
+        <f>_xlfn.XLOOKUP(C105,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <f>_xlfn.XLOOKUP(C105,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <f>_xlfn.XLOOKUP(C105,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <f>_xlfn.XLOOKUP(C105,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <f>_xlfn.XLOOKUP(C105,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <f>_xlfn.XLOOKUP(C105,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="5">
+        <v>105</v>
+      </c>
+      <c r="D106">
+        <f>_xlfn.XLOOKUP(C106,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <f>_xlfn.XLOOKUP(C106,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <f>_xlfn.XLOOKUP(C106,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <f>_xlfn.XLOOKUP(C106,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <f>_xlfn.XLOOKUP(C106,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <f>_xlfn.XLOOKUP(C106,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="5">
+        <v>106</v>
+      </c>
+      <c r="D107">
+        <f>_xlfn.XLOOKUP(C107,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <f>_xlfn.XLOOKUP(C107,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <f>_xlfn.XLOOKUP(C107,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <f>_xlfn.XLOOKUP(C107,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <f>_xlfn.XLOOKUP(C107,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <f>_xlfn.XLOOKUP(C107,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="5">
+        <v>107</v>
+      </c>
+      <c r="D108">
+        <f>_xlfn.XLOOKUP(C108,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <f>_xlfn.XLOOKUP(C108,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <f>_xlfn.XLOOKUP(C108,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <f>_xlfn.XLOOKUP(C108,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <f>_xlfn.XLOOKUP(C108,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <f>_xlfn.XLOOKUP(C108,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="5">
+        <v>108</v>
+      </c>
+      <c r="D109">
+        <f>_xlfn.XLOOKUP(C109,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <f>_xlfn.XLOOKUP(C109,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <f>_xlfn.XLOOKUP(C109,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <f>_xlfn.XLOOKUP(C109,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <f>_xlfn.XLOOKUP(C109,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <f>_xlfn.XLOOKUP(C109,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="5">
+        <v>109</v>
+      </c>
+      <c r="D110">
+        <f>_xlfn.XLOOKUP(C110,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <f>_xlfn.XLOOKUP(C110,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <f>_xlfn.XLOOKUP(C110,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <f>_xlfn.XLOOKUP(C110,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <f>_xlfn.XLOOKUP(C110,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <f>_xlfn.XLOOKUP(C110,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="5">
+        <v>110</v>
+      </c>
+      <c r="D111">
+        <f>_xlfn.XLOOKUP(C111,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <f>_xlfn.XLOOKUP(C111,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <f>_xlfn.XLOOKUP(C111,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <f>_xlfn.XLOOKUP(C111,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <f>_xlfn.XLOOKUP(C111,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <f>_xlfn.XLOOKUP(C111,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="5">
+        <v>111</v>
+      </c>
+      <c r="D112">
+        <f>_xlfn.XLOOKUP(C112,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <f>_xlfn.XLOOKUP(C112,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <f>_xlfn.XLOOKUP(C112,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <f>_xlfn.XLOOKUP(C112,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <f>_xlfn.XLOOKUP(C112,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <f>_xlfn.XLOOKUP(C112,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" s="5">
+        <v>112</v>
+      </c>
+      <c r="D113">
+        <f>_xlfn.XLOOKUP(C113,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <f>_xlfn.XLOOKUP(C113,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <f>_xlfn.XLOOKUP(C113,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <f>_xlfn.XLOOKUP(C113,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <f>_xlfn.XLOOKUP(C113,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <f>_xlfn.XLOOKUP(C113,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="5">
+        <v>113</v>
+      </c>
+      <c r="D114">
+        <f>_xlfn.XLOOKUP(C114,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <f>_xlfn.XLOOKUP(C114,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <f>_xlfn.XLOOKUP(C114,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <f>_xlfn.XLOOKUP(C114,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <f>_xlfn.XLOOKUP(C114,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <f>_xlfn.XLOOKUP(C114,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="5">
+        <v>114</v>
+      </c>
+      <c r="D115">
+        <f>_xlfn.XLOOKUP(C115,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <f>_xlfn.XLOOKUP(C115,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <f>_xlfn.XLOOKUP(C115,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <f>_xlfn.XLOOKUP(C115,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <f>_xlfn.XLOOKUP(C115,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <f>_xlfn.XLOOKUP(C115,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="5">
+        <v>115</v>
+      </c>
+      <c r="D116">
+        <f>_xlfn.XLOOKUP(C116,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <f>_xlfn.XLOOKUP(C116,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <f>_xlfn.XLOOKUP(C116,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <f>_xlfn.XLOOKUP(C116,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <f>_xlfn.XLOOKUP(C116,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <f>_xlfn.XLOOKUP(C116,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="5">
+        <v>116</v>
+      </c>
+      <c r="D117">
+        <f>_xlfn.XLOOKUP(C117,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <f>_xlfn.XLOOKUP(C117,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <f>_xlfn.XLOOKUP(C117,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <f>_xlfn.XLOOKUP(C117,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <f>_xlfn.XLOOKUP(C117,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <f>_xlfn.XLOOKUP(C117,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="5">
+        <v>117</v>
+      </c>
+      <c r="D118">
+        <f>_xlfn.XLOOKUP(C118,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <f>_xlfn.XLOOKUP(C118,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <f>_xlfn.XLOOKUP(C118,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <f>_xlfn.XLOOKUP(C118,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <f>_xlfn.XLOOKUP(C118,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <f>_xlfn.XLOOKUP(C118,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="5">
+        <v>118</v>
+      </c>
+      <c r="D119">
+        <f>_xlfn.XLOOKUP(C119,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <f>_xlfn.XLOOKUP(C119,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <f>_xlfn.XLOOKUP(C119,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <f>_xlfn.XLOOKUP(C119,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <f>_xlfn.XLOOKUP(C119,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <f>_xlfn.XLOOKUP(C119,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="5">
+        <v>119</v>
+      </c>
+      <c r="D120">
+        <f>_xlfn.XLOOKUP(C120,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <f>_xlfn.XLOOKUP(C120,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <f>_xlfn.XLOOKUP(C120,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <f>_xlfn.XLOOKUP(C120,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <f>_xlfn.XLOOKUP(C120,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <f>_xlfn.XLOOKUP(C120,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="5">
+        <v>120</v>
+      </c>
+      <c r="D121">
+        <f>_xlfn.XLOOKUP(C121,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <f>_xlfn.XLOOKUP(C121,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <f>_xlfn.XLOOKUP(C121,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <f>_xlfn.XLOOKUP(C121,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <f>_xlfn.XLOOKUP(C121,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <f>_xlfn.XLOOKUP(C121,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="5">
+        <v>121</v>
+      </c>
+      <c r="D122">
+        <f>_xlfn.XLOOKUP(C122,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <f>_xlfn.XLOOKUP(C122,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <f>_xlfn.XLOOKUP(C122,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <f>_xlfn.XLOOKUP(C122,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <f>_xlfn.XLOOKUP(C122,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <f>_xlfn.XLOOKUP(C122,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="5">
+        <v>122</v>
+      </c>
+      <c r="D123">
+        <f>_xlfn.XLOOKUP(C123,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <f>_xlfn.XLOOKUP(C123,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <f>_xlfn.XLOOKUP(C123,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <f>_xlfn.XLOOKUP(C123,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <f>_xlfn.XLOOKUP(C123,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <f>_xlfn.XLOOKUP(C123,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="5">
+        <v>123</v>
+      </c>
+      <c r="D124">
+        <f>_xlfn.XLOOKUP(C124,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <f>_xlfn.XLOOKUP(C124,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <f>_xlfn.XLOOKUP(C124,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <f>_xlfn.XLOOKUP(C124,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <f>_xlfn.XLOOKUP(C124,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <f>_xlfn.XLOOKUP(C124,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="5">
+        <v>124</v>
+      </c>
+      <c r="D125">
+        <f>_xlfn.XLOOKUP(C125,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <f>_xlfn.XLOOKUP(C125,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <f>_xlfn.XLOOKUP(C125,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <f>_xlfn.XLOOKUP(C125,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <f>_xlfn.XLOOKUP(C125,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <f>_xlfn.XLOOKUP(C125,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="5">
+        <v>125</v>
+      </c>
+      <c r="D126">
+        <f>_xlfn.XLOOKUP(C126,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <f>_xlfn.XLOOKUP(C126,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <f>_xlfn.XLOOKUP(C126,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <f>_xlfn.XLOOKUP(C126,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <f>_xlfn.XLOOKUP(C126,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <f>_xlfn.XLOOKUP(C126,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="5">
+        <v>126</v>
+      </c>
+      <c r="D127">
+        <f>_xlfn.XLOOKUP(C127,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <f>_xlfn.XLOOKUP(C127,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <f>_xlfn.XLOOKUP(C127,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <f>_xlfn.XLOOKUP(C127,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <f>_xlfn.XLOOKUP(C127,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <f>_xlfn.XLOOKUP(C127,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="5">
+        <v>127</v>
+      </c>
+      <c r="D128">
+        <f>_xlfn.XLOOKUP(C128,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <f>_xlfn.XLOOKUP(C128,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <f>_xlfn.XLOOKUP(C128,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <f>_xlfn.XLOOKUP(C128,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <f>_xlfn.XLOOKUP(C128,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <f>_xlfn.XLOOKUP(C128,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" s="5">
+        <v>128</v>
+      </c>
+      <c r="D129">
+        <f>_xlfn.XLOOKUP(C129,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <f>_xlfn.XLOOKUP(C129,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <f>_xlfn.XLOOKUP(C129,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <f>_xlfn.XLOOKUP(C129,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <f>_xlfn.XLOOKUP(C129,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <f>_xlfn.XLOOKUP(C129,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" s="5">
+        <v>129</v>
+      </c>
+      <c r="D130">
+        <f>_xlfn.XLOOKUP(C130,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <f>_xlfn.XLOOKUP(C130,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <f>_xlfn.XLOOKUP(C130,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <f>_xlfn.XLOOKUP(C130,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <f>_xlfn.XLOOKUP(C130,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <f>_xlfn.XLOOKUP(C130,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" s="5">
+        <v>130</v>
+      </c>
+      <c r="D131">
+        <f>_xlfn.XLOOKUP(C131,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <f>_xlfn.XLOOKUP(C131,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <f>_xlfn.XLOOKUP(C131,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <f>_xlfn.XLOOKUP(C131,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <f>_xlfn.XLOOKUP(C131,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <f>_xlfn.XLOOKUP(C131,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" s="5">
+        <v>131</v>
+      </c>
+      <c r="D132">
+        <f>_xlfn.XLOOKUP(C132,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <f>_xlfn.XLOOKUP(C132,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <f>_xlfn.XLOOKUP(C132,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <f>_xlfn.XLOOKUP(C132,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <f>_xlfn.XLOOKUP(C132,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <f>_xlfn.XLOOKUP(C132,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" s="5">
+        <v>132</v>
+      </c>
+      <c r="D133">
+        <f>_xlfn.XLOOKUP(C133,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <f>_xlfn.XLOOKUP(C133,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <f>_xlfn.XLOOKUP(C133,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <f>_xlfn.XLOOKUP(C133,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <f>_xlfn.XLOOKUP(C133,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <f>_xlfn.XLOOKUP(C133,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" s="5">
+        <v>133</v>
+      </c>
+      <c r="D134">
+        <f>_xlfn.XLOOKUP(C134,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <f>_xlfn.XLOOKUP(C134,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <f>_xlfn.XLOOKUP(C134,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <f>_xlfn.XLOOKUP(C134,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <f>_xlfn.XLOOKUP(C134,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <f>_xlfn.XLOOKUP(C134,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" s="5">
+        <v>134</v>
+      </c>
+      <c r="D135">
+        <f>_xlfn.XLOOKUP(C135,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <f>_xlfn.XLOOKUP(C135,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <f>_xlfn.XLOOKUP(C135,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <f>_xlfn.XLOOKUP(C135,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <f>_xlfn.XLOOKUP(C135,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <f>_xlfn.XLOOKUP(C135,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" s="5">
+        <v>135</v>
+      </c>
+      <c r="D136">
+        <f>_xlfn.XLOOKUP(C136,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <f>_xlfn.XLOOKUP(C136,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <f>_xlfn.XLOOKUP(C136,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <f>_xlfn.XLOOKUP(C136,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <f>_xlfn.XLOOKUP(C136,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <f>_xlfn.XLOOKUP(C136,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A137" s="5">
+        <v>136</v>
+      </c>
+      <c r="D137">
+        <f>_xlfn.XLOOKUP(C137,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <f>_xlfn.XLOOKUP(C137,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <f>_xlfn.XLOOKUP(C137,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <f>_xlfn.XLOOKUP(C137,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <f>_xlfn.XLOOKUP(C137,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <f>_xlfn.XLOOKUP(C137,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" s="5">
+        <v>137</v>
+      </c>
+      <c r="D138">
+        <f>_xlfn.XLOOKUP(C138,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <f>_xlfn.XLOOKUP(C138,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <f>_xlfn.XLOOKUP(C138,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <f>_xlfn.XLOOKUP(C138,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <f>_xlfn.XLOOKUP(C138,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <f>_xlfn.XLOOKUP(C138,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" s="5">
+        <v>138</v>
+      </c>
+      <c r="D139">
+        <f>_xlfn.XLOOKUP(C139,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <f>_xlfn.XLOOKUP(C139,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <f>_xlfn.XLOOKUP(C139,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <f>_xlfn.XLOOKUP(C139,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <f>_xlfn.XLOOKUP(C139,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <f>_xlfn.XLOOKUP(C139,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" s="5">
+        <v>139</v>
+      </c>
+      <c r="D140">
+        <f>_xlfn.XLOOKUP(C140,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <f>_xlfn.XLOOKUP(C140,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <f>_xlfn.XLOOKUP(C140,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <f>_xlfn.XLOOKUP(C140,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <f>_xlfn.XLOOKUP(C140,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <f>_xlfn.XLOOKUP(C140,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" s="5">
+        <v>140</v>
+      </c>
+      <c r="D141">
+        <f>_xlfn.XLOOKUP(C141,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <f>_xlfn.XLOOKUP(C141,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <f>_xlfn.XLOOKUP(C141,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <f>_xlfn.XLOOKUP(C141,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <f>_xlfn.XLOOKUP(C141,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <f>_xlfn.XLOOKUP(C141,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A142" s="5">
+        <v>141</v>
+      </c>
+      <c r="D142">
+        <f>_xlfn.XLOOKUP(C142,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <f>_xlfn.XLOOKUP(C142,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <f>_xlfn.XLOOKUP(C142,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <f>_xlfn.XLOOKUP(C142,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <f>_xlfn.XLOOKUP(C142,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <f>_xlfn.XLOOKUP(C142,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" s="5">
+        <v>142</v>
+      </c>
+      <c r="D143">
+        <f>_xlfn.XLOOKUP(C143,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <f>_xlfn.XLOOKUP(C143,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <f>_xlfn.XLOOKUP(C143,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <f>_xlfn.XLOOKUP(C143,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <f>_xlfn.XLOOKUP(C143,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <f>_xlfn.XLOOKUP(C143,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" s="5">
+        <v>143</v>
+      </c>
+      <c r="D144">
+        <f>_xlfn.XLOOKUP(C144,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <f>_xlfn.XLOOKUP(C144,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <f>_xlfn.XLOOKUP(C144,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <f>_xlfn.XLOOKUP(C144,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <f>_xlfn.XLOOKUP(C144,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <f>_xlfn.XLOOKUP(C144,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A145" s="5">
+        <v>144</v>
+      </c>
+      <c r="D145">
+        <f>_xlfn.XLOOKUP(C145,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <f>_xlfn.XLOOKUP(C145,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <f>_xlfn.XLOOKUP(C145,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <f>_xlfn.XLOOKUP(C145,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <f>_xlfn.XLOOKUP(C145,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <f>_xlfn.XLOOKUP(C145,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A146" s="5">
+        <v>145</v>
+      </c>
+      <c r="D146">
+        <f>_xlfn.XLOOKUP(C146,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <f>_xlfn.XLOOKUP(C146,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <f>_xlfn.XLOOKUP(C146,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <f>_xlfn.XLOOKUP(C146,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <f>_xlfn.XLOOKUP(C146,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <f>_xlfn.XLOOKUP(C146,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A147" s="5">
+        <v>146</v>
+      </c>
+      <c r="D147">
+        <f>_xlfn.XLOOKUP(C147,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <f>_xlfn.XLOOKUP(C147,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <f>_xlfn.XLOOKUP(C147,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <f>_xlfn.XLOOKUP(C147,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <f>_xlfn.XLOOKUP(C147,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <f>_xlfn.XLOOKUP(C147,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A148" s="5">
+        <v>147</v>
+      </c>
+      <c r="D148">
+        <f>_xlfn.XLOOKUP(C148,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <f>_xlfn.XLOOKUP(C148,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <f>_xlfn.XLOOKUP(C148,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <f>_xlfn.XLOOKUP(C148,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <f>_xlfn.XLOOKUP(C148,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <f>_xlfn.XLOOKUP(C148,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A149" s="5">
+        <v>148</v>
+      </c>
+      <c r="D149">
+        <f>_xlfn.XLOOKUP(C149,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <f>_xlfn.XLOOKUP(C149,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <f>_xlfn.XLOOKUP(C149,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <f>_xlfn.XLOOKUP(C149,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <f>_xlfn.XLOOKUP(C149,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <f>_xlfn.XLOOKUP(C149,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A150" s="5">
+        <v>149</v>
+      </c>
+      <c r="D150">
+        <f>_xlfn.XLOOKUP(C150,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <f>_xlfn.XLOOKUP(C150,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F150">
+        <f>_xlfn.XLOOKUP(C150,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <f>_xlfn.XLOOKUP(C150,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <f>_xlfn.XLOOKUP(C150,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <f>_xlfn.XLOOKUP(C150,EventTypes!$A:$A,EventTypes!G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A151" s="5">
+        <v>150</v>
+      </c>
+      <c r="D151">
+        <f>_xlfn.XLOOKUP(C151,EventTypes!$A:$A,EventTypes!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <f>_xlfn.XLOOKUP(C151,EventTypes!$A:$A,EventTypes!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="F151">
+        <f>_xlfn.XLOOKUP(C151,EventTypes!$A:$A,EventTypes!C:C)</f>
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <f>_xlfn.XLOOKUP(C151,EventTypes!$A:$A,EventTypes!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <f>_xlfn.XLOOKUP(C151,EventTypes!$A:$A,EventTypes!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <f>_xlfn.XLOOKUP(C151,EventTypes!$A:$A,EventTypes!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -3811,12 +5587,12 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A28E0041-B91F-42DF-A4EA-CAAE5860F066}">
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$17</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C100</xm:sqref>
+          <xm:sqref>C2:C151</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3827,14 +5603,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -3845,7 +5621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3856,7 +5632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3867,7 +5643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3878,7 +5654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3889,7 +5665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3900,7 +5676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3911,7 +5687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3922,7 +5698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3933,7 +5709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3944,7 +5720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3955,7 +5731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3966,7 +5742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3977,7 +5753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3988,7 +5764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3999,7 +5775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4010,7 +5786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4021,7 +5797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4032,7 +5808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4043,7 +5819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4054,7 +5830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4065,7 +5841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4076,7 +5852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4087,7 +5863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4098,7 +5874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4109,7 +5885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4120,7 +5896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4131,7 +5907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4142,7 +5918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4153,7 +5929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4164,7 +5940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4175,7 +5951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4186,7 +5962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4197,7 +5973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4208,7 +5984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4219,7 +5995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4230,7 +6006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4241,7 +6017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4252,7 +6028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4263,7 +6039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4274,7 +6050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4285,7 +6061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4304,21 +6080,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -4414,247 +6190,247 @@
       </c>
       <c r="AF1" s="2"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>Employees!A2</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>Employees!A3</f>
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>Employees!A4</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>Employees!A5</f>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>Employees!A6</f>
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>Employees!A7</f>
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>Employees!A8</f>
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>Employees!A9</f>
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>Employees!A10</f>
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>Employees!A11</f>
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>Employees!A12</f>
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>Employees!A13</f>
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>Employees!A14</f>
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>Employees!A15</f>
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>Employees!A16</f>
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>Employees!A17</f>
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>Employees!A18</f>
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>Employees!A19</f>
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>Employees!A20</f>
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>Employees!A21</f>
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>Employees!A22</f>
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>Employees!A23</f>
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>Employees!A24</f>
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>Employees!A25</f>
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>Employees!A26</f>
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>Employees!A27</f>
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>Employees!A28</f>
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>Employees!A29</f>
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>Employees!A30</f>
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>Employees!A31</f>
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>Employees!A32</f>
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>Employees!A33</f>
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>Employees!A34</f>
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35">
         <f>Employees!A35</f>
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36">
         <f>Employees!A36</f>
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37">
         <f>Employees!A37</f>
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38">
         <f>Employees!A38</f>
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39">
         <f>Employees!A39</f>
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40">
         <f>Employees!A40</f>
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41">
         <f>Employees!A41</f>
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42">
         <f>Employees!A42</f>
         <v>41</v>
@@ -4668,54 +6444,54 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ60"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.08984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.77734375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="6" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4889,7 +6665,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>Events!B2</f>
         <v>0</v>
@@ -4899,7 +6675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>Events!B3</f>
         <v>0</v>
@@ -4909,7 +6685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>Events!B4</f>
         <v>0</v>
@@ -4919,7 +6695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>Events!B5</f>
         <v>0</v>
@@ -4929,7 +6705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>Events!B6</f>
         <v>0</v>
@@ -4939,7 +6715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>Events!B7</f>
         <v>0</v>
@@ -4949,7 +6725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>Events!B8</f>
         <v>0</v>
@@ -4959,7 +6735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>Events!B9</f>
         <v>0</v>
@@ -4969,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>Events!B10</f>
         <v>0</v>
@@ -4979,7 +6755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>Events!B11</f>
         <v>0</v>
@@ -4989,7 +6765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>Events!B12</f>
         <v>0</v>
@@ -4999,7 +6775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>Events!B13</f>
         <v>0</v>
@@ -5009,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>Events!B14</f>
         <v>0</v>
@@ -5019,7 +6795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>Events!B15</f>
         <v>0</v>
@@ -5029,7 +6805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>Events!B16</f>
         <v>0</v>
@@ -5039,7 +6815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>Events!B17</f>
         <v>0</v>
@@ -5049,7 +6825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>Events!B18</f>
         <v>0</v>
@@ -5059,7 +6835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>Events!B19</f>
         <v>0</v>
@@ -5069,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>Events!B20</f>
         <v>0</v>
@@ -5079,7 +6855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>Events!B21</f>
         <v>0</v>
@@ -5089,7 +6865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>Events!B22</f>
         <v>0</v>
@@ -5099,7 +6875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>Events!B23</f>
         <v>0</v>
@@ -5109,7 +6885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>Events!B24</f>
         <v>0</v>
@@ -5119,7 +6895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>Events!B25</f>
         <v>0</v>
@@ -5129,7 +6905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>Events!B26</f>
         <v>0</v>
@@ -5139,7 +6915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>Events!B27</f>
         <v>0</v>
@@ -5149,7 +6925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>Events!B28</f>
         <v>0</v>
@@ -5159,7 +6935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>Events!B29</f>
         <v>0</v>
@@ -5169,7 +6945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>Events!B30</f>
         <v>0</v>
@@ -5179,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>Events!B31</f>
         <v>0</v>
@@ -5189,7 +6965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>Events!B32</f>
         <v>0</v>
@@ -5199,7 +6975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>Events!B33</f>
         <v>0</v>
@@ -5209,7 +6985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>Events!B34</f>
         <v>0</v>
@@ -5219,7 +6995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <f>Events!B35</f>
         <v>0</v>
@@ -5229,7 +7005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <f>Events!B36</f>
         <v>0</v>
@@ -5239,7 +7015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <f>Events!B37</f>
         <v>0</v>
@@ -5249,7 +7025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <f>Events!B38</f>
         <v>0</v>
@@ -5259,7 +7035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <f>Events!B39</f>
         <v>0</v>
@@ -5269,7 +7045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <f>Events!B40</f>
         <v>0</v>
@@ -5279,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <f>Events!B41</f>
         <v>0</v>
@@ -5289,7 +7065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <f>Events!B42</f>
         <v>0</v>
@@ -5299,7 +7075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <f>Events!B43</f>
         <v>0</v>
@@ -5309,7 +7085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <f>Events!B44</f>
         <v>0</v>
@@ -5319,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <f>Events!B45</f>
         <v>0</v>
@@ -5329,7 +7105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <f>Events!B46</f>
         <v>0</v>
@@ -5339,7 +7115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <f>Events!B47</f>
         <v>0</v>
@@ -5349,7 +7125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <f>Events!B48</f>
         <v>0</v>
@@ -5359,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <f>Events!B49</f>
         <v>0</v>
@@ -5369,7 +7145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <f>Events!B50</f>
         <v>0</v>
@@ -5379,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <f>Events!B51</f>
         <v>0</v>
@@ -5389,7 +7165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <f>Events!B52</f>
         <v>0</v>
@@ -5399,7 +7175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <f>Events!B53</f>
         <v>0</v>
@@ -5409,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <f>Events!B54</f>
         <v>0</v>
@@ -5419,7 +7195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <f>Events!B55</f>
         <v>0</v>
@@ -5429,7 +7205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <f>Events!B56</f>
         <v>0</v>
@@ -5439,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <f>Events!B57</f>
         <v>0</v>
@@ -5449,7 +7225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <f>Events!B58</f>
         <v>0</v>
@@ -5459,7 +7235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <f>Events!B59</f>
         <v>0</v>
@@ -5469,7 +7245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <f>Events!B60</f>
         <v>0</v>
@@ -5487,17 +7263,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5520,7 +7296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5543,7 +7319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5566,7 +7342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5589,7 +7365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5612,7 +7388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5635,7 +7411,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5658,7 +7434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5681,7 +7457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5704,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5727,7 +7503,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5750,7 +7526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -5773,7 +7549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5796,7 +7572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5819,7 +7595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5842,7 +7618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5865,7 +7641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -5881,14 +7657,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.08984375" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -5899,7 +7675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5910,7 +7686,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5921,7 +7697,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5932,7 +7708,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5943,7 +7719,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5954,7 +7730,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5965,7 +7741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5976,7 +7752,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5987,7 +7763,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -6006,12 +7782,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -6022,7 +7798,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -6033,7 +7809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -6044,7 +7820,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -6055,7 +7831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -6066,7 +7842,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -6077,7 +7853,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -6089,7 +7865,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -6100,7 +7876,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -6111,7 +7887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -6122,7 +7898,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -6133,7 +7909,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -6144,7 +7920,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -6155,7 +7931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -6166,7 +7942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -6177,7 +7953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -6188,7 +7964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -6199,7 +7975,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -6210,7 +7986,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -6221,7 +7997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -6232,7 +8008,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -6243,7 +8019,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -6254,7 +8030,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -6265,7 +8041,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -6276,7 +8052,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -6287,7 +8063,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -6299,7 +8075,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -6311,7 +8087,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -6323,7 +8099,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -6334,7 +8110,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -6345,7 +8121,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -6356,7 +8132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -6367,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -6378,7 +8154,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -6389,7 +8165,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>46</v>
       </c>
